--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484310_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484310_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.3522</v>
+        <v>6.0096</v>
       </c>
       <c r="E2" t="n">
-        <v>3.7525</v>
+        <v>4.0559</v>
       </c>
       <c r="F2" t="n">
-        <v>1.5996</v>
+        <v>1.9537</v>
       </c>
       <c r="G2" t="n">
         <v>1.157</v>
@@ -610,13 +610,13 @@
         <v>2.1488</v>
       </c>
       <c r="S2" t="n">
-        <v>0.3792</v>
+        <v>1.0366</v>
       </c>
       <c r="T2" t="n">
-        <v>0.5973000000000001</v>
+        <v>0.9006</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.2181</v>
+        <v>0.136</v>
       </c>
       <c r="V2" t="n">
         <v>4.5973</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.0272</v>
+        <v>1.9227</v>
       </c>
       <c r="E3" t="n">
-        <v>4.4322</v>
+        <v>3.2189</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.4051</v>
+        <v>-1.2961</v>
       </c>
       <c r="G3" t="n">
         <v>2.5216</v>
@@ -688,13 +688,13 @@
         <v>0.9767</v>
       </c>
       <c r="S3" t="n">
-        <v>2.9781</v>
+        <v>1.8737</v>
       </c>
       <c r="T3" t="n">
-        <v>2.5507</v>
+        <v>1.3374</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4274</v>
+        <v>0.5364</v>
       </c>
       <c r="V3" t="n">
         <v>-1.4959</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>2.3518</v>
+        <v>0.909</v>
       </c>
       <c r="E4" t="n">
-        <v>2.9338</v>
+        <v>1.5182</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.582</v>
+        <v>-0.6092</v>
       </c>
       <c r="G4" t="n">
         <v>0.9627</v>
@@ -766,13 +766,13 @@
         <v>1.1721</v>
       </c>
       <c r="S4" t="n">
-        <v>1.7483</v>
+        <v>0.3054</v>
       </c>
       <c r="T4" t="n">
-        <v>2.1049</v>
+        <v>0.6893</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3567</v>
+        <v>-0.3839</v>
       </c>
       <c r="V4" t="n">
         <v>-0.5545</v>
@@ -799,13 +799,13 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-0.3102</v>
+        <v>0.6778</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.4582</v>
+        <v>-0.8515</v>
       </c>
       <c r="F5" t="n">
-        <v>1.148</v>
+        <v>1.5293</v>
       </c>
       <c r="G5" t="n">
         <v>-1.6705</v>
@@ -844,13 +844,13 @@
         <v>1.5627</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.2024</v>
+        <v>0.7855</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1653</v>
+        <v>0.772</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.3677</v>
+        <v>0.0136</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.4784</v>
+        <v>-0.3229</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.0263</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.4522</v>
+        <v>-0.3977</v>
       </c>
       <c r="G6" t="n">
         <v>-0.6633</v>
@@ -922,13 +922,13 @@
         <v>0.1953</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.0104</v>
+        <v>0.1452</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.0467</v>
+        <v>0.0544</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0363</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V6" t="n">
         <v>0</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.6655</v>
+        <v>-0.7318</v>
       </c>
       <c r="E7" t="n">
-        <v>-2.1456</v>
+        <v>-1.64</v>
       </c>
       <c r="F7" t="n">
-        <v>1.4801</v>
+        <v>0.9082</v>
       </c>
       <c r="G7" t="n">
         <v>-4.7951</v>
@@ -1000,13 +1000,13 @@
         <v>0.9767</v>
       </c>
       <c r="S7" t="n">
-        <v>1.4152</v>
+        <v>1.3488</v>
       </c>
       <c r="T7" t="n">
-        <v>0.4679</v>
+        <v>0.9735</v>
       </c>
       <c r="U7" t="n">
-        <v>0.9473</v>
+        <v>0.3753</v>
       </c>
       <c r="V7" t="n">
         <v>2.7145</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.8856000000000001</v>
+        <v>-1.0061</v>
       </c>
       <c r="E8" t="n">
-        <v>0.8555</v>
+        <v>0.6533</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.7411</v>
+        <v>-1.6594</v>
       </c>
       <c r="G8" t="n">
         <v>-0.5441</v>
@@ -1078,13 +1078,13 @@
         <v>0.586</v>
       </c>
       <c r="S8" t="n">
-        <v>0.2911</v>
+        <v>0.1706</v>
       </c>
       <c r="T8" t="n">
-        <v>0.5063</v>
+        <v>0.3041</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.2152</v>
+        <v>-0.1335</v>
       </c>
       <c r="V8" t="n">
         <v>-1.2186</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,67 +1111,67 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.9254</v>
+        <v>-1.8342</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.8423</v>
+        <v>0.4454</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.08309999999999999</v>
+        <v>-2.2796</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.6982</v>
+        <v>-0.901</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.2553</v>
+        <v>-0.8066</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.4429</v>
+        <v>-0.0944</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.2041</v>
+        <v>-0.5518</v>
       </c>
       <c r="K9" t="n">
-        <v>0.1036</v>
+        <v>0.0819</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.3077</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.4941</v>
+        <v>-0.3492</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.3589</v>
+        <v>-0.8885</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.1352</v>
+        <v>0.5393</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q9" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>0.6361</v>
+        <v>-0.4141</v>
       </c>
       <c r="T9" t="n">
-        <v>0.3385</v>
+        <v>-0.2214</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2976</v>
+        <v>-0.1926</v>
       </c>
       <c r="V9" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X9" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
       </c>
     </row>
     <row r="10">
@@ -1189,10 +1189,10 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.9816</v>
+        <v>-1.8805</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.9629</v>
+        <v>-0.8618</v>
       </c>
       <c r="F10" t="n">
         <v>-1.0186</v>
@@ -1234,10 +1234,10 @@
         <v>0</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.121</v>
+        <v>-0.0199</v>
       </c>
       <c r="T10" t="n">
-        <v>0.0138</v>
+        <v>0.1149</v>
       </c>
       <c r="U10" t="n">
         <v>-0.1348</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.9819</v>
+        <v>-1.972</v>
       </c>
       <c r="E11" t="n">
-        <v>0.2432</v>
+        <v>-1.9435</v>
       </c>
       <c r="F11" t="n">
-        <v>-2.2251</v>
+        <v>-0.0286</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.901</v>
+        <v>-1.6982</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.8066</v>
+        <v>-0.2553</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.0944</v>
+        <v>-1.4429</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.5518</v>
+        <v>-1.2041</v>
       </c>
       <c r="K11" t="n">
-        <v>0.0819</v>
+        <v>0.1036</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-1.3077</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.3492</v>
+        <v>-0.4941</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.8885</v>
+        <v>-0.3589</v>
       </c>
       <c r="O11" t="n">
-        <v>0.5393</v>
+        <v>-0.1352</v>
       </c>
       <c r="P11" t="n">
-        <v>0.9767</v>
+        <v>-0.586</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R11" t="n">
-        <v>0.9767</v>
+        <v>0.3907</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5618</v>
+        <v>0.5895</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.4237</v>
+        <v>0.2374</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.1382</v>
+        <v>0.3521</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.4959</v>
+        <v>-0.2772</v>
       </c>
       <c r="W11" t="n">
-        <v>1.2186</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7145</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-3.3172</v>
+        <v>-2.5862</v>
       </c>
       <c r="E12" t="n">
-        <v>-5.6078</v>
+        <v>-4.4955</v>
       </c>
       <c r="F12" t="n">
-        <v>2.2906</v>
+        <v>1.9093</v>
       </c>
       <c r="G12" t="n">
         <v>-1.9468</v>
@@ -1390,13 +1390,13 @@
         <v>1.7581</v>
       </c>
       <c r="S12" t="n">
-        <v>0.1887</v>
+        <v>0.9196</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.5226</v>
+        <v>0.5897</v>
       </c>
       <c r="U12" t="n">
-        <v>0.7112000000000001</v>
+        <v>0.3299</v>
       </c>
       <c r="V12" t="n">
         <v>-0.3869</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8146000000000013</v>
+        <v>-0.8145999999999995</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1740999999999993</v>
+        <v>0.1742000000000008</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9889000000000001</v>
+        <v>-0.9886999999999997</v>
       </c>
       <c r="G13" t="n">
         <v>-8.461499999999999</v>
@@ -1441,10 +1441,10 @@
         <v>1.3492</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.7735</v>
+        <v>-3.773500000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2669999999999997</v>
+        <v>0.2669999999999995</v>
       </c>
       <c r="L13" t="n">
         <v>-4.0406</v>
@@ -1456,7 +1456,7 @@
         <v>-10.0779</v>
       </c>
       <c r="O13" t="n">
-        <v>5.3898</v>
+        <v>5.389799999999999</v>
       </c>
       <c r="P13" t="n">
         <v>-0.9768999999999999</v>
@@ -1468,13 +1468,13 @@
         <v>10.7438</v>
       </c>
       <c r="S13" t="n">
-        <v>6.7411</v>
+        <v>6.7409</v>
       </c>
       <c r="T13" t="n">
-        <v>5.7517</v>
+        <v>5.751899999999999</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9891000000000001</v>
+        <v>0.9893000000000001</v>
       </c>
       <c r="V13" t="n">
         <v>1.8828</v>
@@ -1483,7 +1483,7 @@
         <v>9.916499999999999</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.0337</v>
+        <v>-8.033700000000001</v>
       </c>
     </row>
     <row r="14">
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.9736</v>
+        <v>7.5973</v>
       </c>
       <c r="E14" t="n">
         <v>7.1572</v>
       </c>
       <c r="F14" t="n">
-        <v>-0.1836</v>
+        <v>0.4401</v>
       </c>
       <c r="G14" t="n">
         <v>5.2971</v>
@@ -1546,13 +1546,13 @@
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-2.0613</v>
+        <v>-1.4376</v>
       </c>
       <c r="T14" t="n">
         <v>-0.5088</v>
       </c>
       <c r="U14" t="n">
-        <v>-1.5525</v>
+        <v>-0.9288</v>
       </c>
       <c r="V14" t="n">
         <v>3.9331</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.2993</v>
+        <v>3.5274</v>
       </c>
       <c r="E15" t="n">
-        <v>1.8139</v>
+        <v>2.0162</v>
       </c>
       <c r="F15" t="n">
-        <v>1.4854</v>
+        <v>1.5113</v>
       </c>
       <c r="G15" t="n">
         <v>0.2996</v>
@@ -1624,13 +1624,13 @@
         <v>1.7581</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.2542</v>
+        <v>-0.0261</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.1457</v>
+        <v>0.0566</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.1085</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V15" t="n">
         <v>1.4959</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1657,73 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.3103</v>
+        <v>1.2558</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.9867</v>
+        <v>0.3084</v>
       </c>
       <c r="F16" t="n">
-        <v>2.297</v>
+        <v>0.9474</v>
       </c>
       <c r="G16" t="n">
-        <v>3.2193</v>
+        <v>0.9883</v>
       </c>
       <c r="H16" t="n">
-        <v>2.02</v>
+        <v>0.8534</v>
       </c>
       <c r="I16" t="n">
-        <v>1.1994</v>
+        <v>0.1348</v>
       </c>
       <c r="J16" t="n">
-        <v>2.4596</v>
+        <v>0.3888</v>
       </c>
       <c r="K16" t="n">
-        <v>2.3382</v>
+        <v>0.3888</v>
       </c>
       <c r="L16" t="n">
-        <v>0.1214</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>0.7598</v>
+        <v>0.5994</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.3182</v>
+        <v>0.4646</v>
       </c>
       <c r="O16" t="n">
-        <v>1.078</v>
+        <v>0.1348</v>
       </c>
       <c r="P16" t="n">
-        <v>-1.5627</v>
+        <v>0.3907</v>
       </c>
       <c r="Q16" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R16" t="n">
-        <v>2.3441</v>
+        <v>0.3907</v>
       </c>
       <c r="S16" t="n">
-        <v>0.263</v>
+        <v>-0.1231</v>
       </c>
       <c r="T16" t="n">
-        <v>0.7926</v>
+        <v>-0.0805</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.5296999999999999</v>
+        <v>-0.0427</v>
       </c>
       <c r="V16" t="n">
-        <v>-0.6093</v>
+        <v>0</v>
       </c>
       <c r="W16" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="X16" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,67 +1735,67 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.8837</v>
+        <v>0.6256</v>
       </c>
       <c r="E17" t="n">
-        <v>0.2073</v>
+        <v>-1.6945</v>
       </c>
       <c r="F17" t="n">
-        <v>0.6764</v>
+        <v>2.3201</v>
       </c>
       <c r="G17" t="n">
-        <v>0.9883</v>
+        <v>3.2193</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8534</v>
+        <v>2.02</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1348</v>
+        <v>1.1994</v>
       </c>
       <c r="J17" t="n">
-        <v>0.3888</v>
+        <v>2.4596</v>
       </c>
       <c r="K17" t="n">
-        <v>0.3888</v>
+        <v>2.3382</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>0.1214</v>
       </c>
       <c r="M17" t="n">
-        <v>0.5994</v>
+        <v>0.7598</v>
       </c>
       <c r="N17" t="n">
-        <v>0.4646</v>
+        <v>-0.3182</v>
       </c>
       <c r="O17" t="n">
-        <v>0.1348</v>
+        <v>1.078</v>
       </c>
       <c r="P17" t="n">
-        <v>0.3907</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q17" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R17" t="n">
-        <v>0.3907</v>
+        <v>2.3441</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4952</v>
+        <v>-0.4217</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.1816</v>
+        <v>0.0848</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.3137</v>
+        <v>-0.5065</v>
       </c>
       <c r="V17" t="n">
-        <v>0</v>
+        <v>-0.6093</v>
       </c>
       <c r="W17" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X17" t="n">
-        <v>0</v>
+        <v>-0.2772</v>
       </c>
     </row>
     <row r="18">
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0115</v>
+        <v>0.5693</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1758</v>
+        <v>1.378</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.1873</v>
+        <v>-0.8087</v>
       </c>
       <c r="G18" t="n">
         <v>1.9458</v>
@@ -1858,13 +1858,13 @@
         <v>0.7814</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.4847</v>
+        <v>-0.9039</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.7125</v>
+        <v>-0.5103</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7722</v>
+        <v>-0.3936</v>
       </c>
       <c r="V18" t="n">
         <v>-0.2772</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0641</v>
+        <v>-0.6435</v>
       </c>
       <c r="E19" t="n">
-        <v>0.8947000000000001</v>
+        <v>0.288</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9588</v>
+        <v>-0.9315</v>
       </c>
       <c r="G19" t="n">
         <v>-0.3604</v>
@@ -1936,13 +1936,13 @@
         <v>0.586</v>
       </c>
       <c r="S19" t="n">
-        <v>0.9288999999999999</v>
+        <v>0.3495</v>
       </c>
       <c r="T19" t="n">
-        <v>1.1804</v>
+        <v>0.5737</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2515</v>
+        <v>-0.2242</v>
       </c>
       <c r="V19" t="n">
         <v>-1.2186</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.4394</v>
+        <v>-1.3665</v>
       </c>
       <c r="E20" t="n">
-        <v>0.5728</v>
+        <v>-0.135</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.0123</v>
+        <v>-1.2315</v>
       </c>
       <c r="G20" t="n">
         <v>1.6519</v>
@@ -2014,13 +2014,13 @@
         <v>0.9767</v>
       </c>
       <c r="S20" t="n">
-        <v>0.9552</v>
+        <v>0.0282</v>
       </c>
       <c r="T20" t="n">
-        <v>0.7567</v>
+        <v>0.0489</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1985</v>
+        <v>-0.0208</v>
       </c>
       <c r="V20" t="n">
         <v>-3.0466</v>
@@ -2035,7 +2035,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>P. MONÉS RIERA</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,73 +2047,73 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.6064</v>
+        <v>-2.1656</v>
       </c>
       <c r="E21" t="n">
-        <v>-1.5494</v>
+        <v>-3.2881</v>
       </c>
       <c r="F21" t="n">
-        <v>-1.057</v>
+        <v>1.1225</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.3868</v>
+        <v>-1.8665</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.1734</v>
+        <v>-0.2346</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.2134</v>
+        <v>-1.6319</v>
       </c>
       <c r="J21" t="n">
-        <v>-1.3073</v>
+        <v>-2.5661</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0409</v>
+        <v>0.0089</v>
       </c>
       <c r="L21" t="n">
-        <v>-1.3482</v>
+        <v>-2.575</v>
       </c>
       <c r="M21" t="n">
-        <v>-0.0795</v>
+        <v>0.6997</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2144</v>
+        <v>-0.2435</v>
       </c>
       <c r="O21" t="n">
-        <v>0.1348</v>
+        <v>0.9431</v>
       </c>
       <c r="P21" t="n">
-        <v>0</v>
+        <v>0.9767</v>
       </c>
       <c r="Q21" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R21" t="n">
-        <v>0</v>
+        <v>1.9534</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.6102</v>
+        <v>-0.9437</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2421</v>
+        <v>-0.2997</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3681</v>
+        <v>-0.6441</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.6093</v>
+        <v>-0.3321</v>
       </c>
       <c r="W21" t="n">
-        <v>0</v>
+        <v>0.5545</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.6093</v>
+        <v>-0.8865</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>P. MONÉS RIERA</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,67 +2125,67 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2441</v>
+        <v>-2.316</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.097</v>
+        <v>-1.4482</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8528</v>
+        <v>-0.8677</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.8665</v>
+        <v>-1.3868</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.2346</v>
+        <v>-0.1734</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.6319</v>
+        <v>-1.2134</v>
       </c>
       <c r="J22" t="n">
-        <v>-2.5661</v>
+        <v>-1.3073</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0089</v>
+        <v>0.0409</v>
       </c>
       <c r="L22" t="n">
-        <v>-2.575</v>
+        <v>-1.3482</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6997</v>
+        <v>-0.0795</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2435</v>
+        <v>-0.2144</v>
       </c>
       <c r="O22" t="n">
-        <v>0.9431</v>
+        <v>0.1348</v>
       </c>
       <c r="P22" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q22" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S22" t="n">
-        <v>-2.0223</v>
+        <v>-0.3198</v>
       </c>
       <c r="T22" t="n">
-        <v>-1.1086</v>
+        <v>-0.141</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.9137</v>
+        <v>-0.1789</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.3321</v>
+        <v>-0.6093</v>
       </c>
       <c r="W22" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.8865</v>
+        <v>-0.6093</v>
       </c>
     </row>
     <row r="23">
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-5.2868</v>
+        <v>-4.247</v>
       </c>
       <c r="E23" t="n">
-        <v>-4.1999</v>
+        <v>-3.5932</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.0869</v>
+        <v>-0.6538</v>
       </c>
       <c r="G23" t="n">
         <v>-1.3267</v>
@@ -2248,13 +2248,13 @@
         <v>1.1721</v>
       </c>
       <c r="S23" t="n">
-        <v>-1.9601</v>
+        <v>-0.9204</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.8198</v>
+        <v>-0.2131</v>
       </c>
       <c r="U23" t="n">
-        <v>-1.1403</v>
+        <v>-0.7073</v>
       </c>
       <c r="V23" t="n">
         <v>-1.2186</v>
@@ -2281,31 +2281,31 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>0.8145999999999995</v>
+        <v>2.836800000000001</v>
       </c>
       <c r="E24" t="n">
-        <v>0.9886999999999979</v>
+        <v>0.988799999999999</v>
       </c>
       <c r="F24" t="n">
-        <v>-0.1743000000000008</v>
+        <v>1.8482</v>
       </c>
       <c r="G24" t="n">
-        <v>8.461600000000001</v>
+        <v>8.461599999999999</v>
       </c>
       <c r="H24" t="n">
-        <v>9.8109</v>
+        <v>9.810899999999998</v>
       </c>
       <c r="I24" t="n">
         <v>-1.349299999999999</v>
       </c>
       <c r="J24" t="n">
-        <v>4.687999999999999</v>
+        <v>4.688</v>
       </c>
       <c r="K24" t="n">
         <v>10.0778</v>
       </c>
       <c r="L24" t="n">
-        <v>-5.389800000000001</v>
+        <v>-5.3898</v>
       </c>
       <c r="M24" t="n">
         <v>3.7737</v>
@@ -2326,13 +2326,13 @@
         <v>11.7206</v>
       </c>
       <c r="S24" t="n">
-        <v>-6.740899999999999</v>
+        <v>-4.7186</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9894000000000002</v>
+        <v>-0.9894000000000001</v>
       </c>
       <c r="U24" t="n">
-        <v>-5.7517</v>
+        <v>-3.7295</v>
       </c>
       <c r="V24" t="n">
         <v>-1.8827</v>
@@ -2341,7 +2341,7 @@
         <v>8.033799999999999</v>
       </c>
       <c r="X24" t="n">
-        <v>-9.916400000000001</v>
+        <v>-9.916399999999999</v>
       </c>
     </row>
   </sheetData>

--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484310_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484310_PROCESSED_CHRONO.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X24"/>
+  <dimension ref="A1:Y27"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -549,6 +549,11 @@
           <t>Def_FT</t>
         </is>
       </c>
+      <c r="Y1" s="1" t="inlineStr">
+        <is>
+          <t>Game_File</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -627,6 +632,11 @@
       <c r="X2" t="n">
         <v>-0.2772</v>
       </c>
+      <c r="Y2" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -705,11 +715,16 @@
       <c r="X3" t="n">
         <v>-2.7145</v>
       </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>U. FERNANDEZ RUIZ</t>
+          <t>G. PÉREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +736,78 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.909</v>
+        <v>1.221</v>
       </c>
       <c r="E4" t="n">
-        <v>1.5182</v>
+        <v>1.221</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.6092</v>
+        <v>0</v>
       </c>
       <c r="G4" t="n">
-        <v>0.9627</v>
+        <v>1.221</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.1563</v>
+        <v>0.614</v>
       </c>
       <c r="I4" t="n">
-        <v>1.119</v>
+        <v>0.607</v>
       </c>
       <c r="J4" t="n">
-        <v>1.8056</v>
+        <v>1.221</v>
       </c>
       <c r="K4" t="n">
-        <v>1.7651</v>
+        <v>0.614</v>
       </c>
       <c r="L4" t="n">
-        <v>0.0405</v>
+        <v>0.607</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.8429</v>
+        <v>0</v>
       </c>
       <c r="N4" t="n">
-        <v>-1.9215</v>
+        <v>0</v>
       </c>
       <c r="O4" t="n">
-        <v>1.0786</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
-        <v>0.1953</v>
+        <v>0</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R4" t="n">
-        <v>1.1721</v>
+        <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>0.3054</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
-        <v>0.6893</v>
+        <v>0</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.3839</v>
+        <v>0</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5545</v>
+        <v>0</v>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>G. PÉREZ LAYUNTA</t>
+          <t>R. PÉREZ GALINDO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +819,78 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.6778</v>
+        <v>0.914</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.8515</v>
+        <v>0.914</v>
       </c>
       <c r="F5" t="n">
-        <v>1.5293</v>
+        <v>0</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.6705</v>
+        <v>0.914</v>
       </c>
       <c r="H5" t="n">
-        <v>-1.8995</v>
+        <v>0.307</v>
       </c>
       <c r="I5" t="n">
-        <v>0.229</v>
+        <v>0.607</v>
       </c>
       <c r="J5" t="n">
-        <v>-1.9007</v>
+        <v>0.914</v>
       </c>
       <c r="K5" t="n">
-        <v>-1.3214</v>
+        <v>0.307</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.5794</v>
+        <v>0.607</v>
       </c>
       <c r="M5" t="n">
-        <v>0.2302</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.5780999999999999</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>0.8083</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
         <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.5627</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.7855</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>0.772</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0136</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
         <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>0.2772</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>M. FENÉS HERNÁNDEZ</t>
+          <t>U. FERNANDEZ RUIZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,73 +902,78 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.3229</v>
+        <v>0.909</v>
       </c>
       <c r="E6" t="n">
-        <v>0.07480000000000001</v>
+        <v>1.5182</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.3977</v>
+        <v>-0.6092</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.6633</v>
+        <v>0.9627</v>
       </c>
       <c r="H6" t="n">
-        <v>-0.7982</v>
+        <v>-0.1563</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1348</v>
+        <v>1.119</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0205</v>
+        <v>1.8056</v>
       </c>
       <c r="K6" t="n">
-        <v>0.0205</v>
+        <v>1.7651</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>0.0405</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.6838</v>
+        <v>-0.8429</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.8186</v>
+        <v>-1.9215</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1348</v>
+        <v>1.0786</v>
       </c>
       <c r="P6" t="n">
         <v>0.1953</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R6" t="n">
-        <v>0.1953</v>
+        <v>1.1721</v>
       </c>
       <c r="S6" t="n">
-        <v>0.1452</v>
+        <v>0.3054</v>
       </c>
       <c r="T6" t="n">
-        <v>0.0544</v>
+        <v>0.6893</v>
       </c>
       <c r="U6" t="n">
-        <v>0.09080000000000001</v>
+        <v>-0.3839</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.5545</v>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>G. RUBIO GRACIA</t>
+          <t>M. FENES HERNANDEZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,73 +985,78 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.7318</v>
+        <v>-0.3229</v>
       </c>
       <c r="E7" t="n">
-        <v>-1.64</v>
+        <v>0.07480000000000001</v>
       </c>
       <c r="F7" t="n">
-        <v>0.9082</v>
+        <v>-0.3977</v>
       </c>
       <c r="G7" t="n">
-        <v>-4.7951</v>
+        <v>-0.6633</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.7746</v>
+        <v>-0.7982</v>
       </c>
       <c r="I7" t="n">
-        <v>-3.0205</v>
+        <v>0.1348</v>
       </c>
       <c r="J7" t="n">
-        <v>-4.3512</v>
+        <v>0.0205</v>
       </c>
       <c r="K7" t="n">
-        <v>-1.0617</v>
+        <v>0.0205</v>
       </c>
       <c r="L7" t="n">
-        <v>-3.2896</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>-0.4439</v>
+        <v>-0.6838</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7129</v>
+        <v>-0.8186</v>
       </c>
       <c r="O7" t="n">
-        <v>0.269</v>
+        <v>0.1348</v>
       </c>
       <c r="P7" t="n">
-        <v>0</v>
+        <v>0.1953</v>
       </c>
       <c r="Q7" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.9767</v>
+        <v>0.1953</v>
       </c>
       <c r="S7" t="n">
-        <v>1.3488</v>
+        <v>0.1452</v>
       </c>
       <c r="T7" t="n">
-        <v>0.9735</v>
+        <v>0.0544</v>
       </c>
       <c r="U7" t="n">
-        <v>0.3753</v>
+        <v>0.09080000000000001</v>
       </c>
       <c r="V7" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>2.7145</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
         <v>0</v>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>P. MARTÍNEZ FERIA</t>
+          <t>G. PEREZ LAYUNTA</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,73 +1068,78 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.0061</v>
+        <v>-0.5432</v>
       </c>
       <c r="E8" t="n">
-        <v>0.6533</v>
+        <v>-2.0725</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.6594</v>
+        <v>1.5293</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.5441</v>
+        <v>-2.8915</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.8138</v>
+        <v>-2.5135</v>
       </c>
       <c r="I8" t="n">
-        <v>0.2696</v>
+        <v>-0.378</v>
       </c>
       <c r="J8" t="n">
-        <v>0.3492</v>
+        <v>-3.1217</v>
       </c>
       <c r="K8" t="n">
-        <v>0.3492</v>
+        <v>-1.9354</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>-1.1863</v>
       </c>
       <c r="M8" t="n">
-        <v>-0.8933</v>
+        <v>0.2302</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.163</v>
+        <v>-0.5780999999999999</v>
       </c>
       <c r="O8" t="n">
-        <v>0.2696</v>
+        <v>0.8083</v>
       </c>
       <c r="P8" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="Q8" t="n">
         <v>0</v>
       </c>
       <c r="R8" t="n">
-        <v>0.586</v>
+        <v>1.5627</v>
       </c>
       <c r="S8" t="n">
-        <v>0.1706</v>
+        <v>0.7855</v>
       </c>
       <c r="T8" t="n">
-        <v>0.3041</v>
+        <v>0.772</v>
       </c>
       <c r="U8" t="n">
-        <v>-0.1335</v>
+        <v>0.0136</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
       </c>
       <c r="W8" t="n">
-        <v>0</v>
+        <v>0.2772</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>B. ROS FERNANDEZ</t>
+          <t>G. RUBIO GRACIA</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1151,78 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.8342</v>
+        <v>-0.7318</v>
       </c>
       <c r="E9" t="n">
-        <v>0.4454</v>
+        <v>-1.64</v>
       </c>
       <c r="F9" t="n">
-        <v>-2.2796</v>
+        <v>0.9082</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.901</v>
+        <v>-4.7951</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.8066</v>
+        <v>-1.7746</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.0944</v>
+        <v>-3.0205</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.5518</v>
+        <v>-4.3512</v>
       </c>
       <c r="K9" t="n">
-        <v>0.0819</v>
+        <v>-1.0617</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6336000000000001</v>
+        <v>-3.2896</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.3492</v>
+        <v>-0.4439</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.8885</v>
+        <v>-0.7129</v>
       </c>
       <c r="O9" t="n">
-        <v>0.5393</v>
+        <v>0.269</v>
       </c>
       <c r="P9" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-0.9767</v>
       </c>
       <c r="R9" t="n">
         <v>0.9767</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.4141</v>
+        <v>1.3488</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.2214</v>
+        <v>0.9735</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1926</v>
+        <v>0.3753</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.4959</v>
+        <v>2.7145</v>
       </c>
       <c r="W9" t="n">
-        <v>1.2186</v>
+        <v>2.7145</v>
       </c>
       <c r="X9" t="n">
-        <v>-2.7145</v>
+        <v>0</v>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>P. MONSALVE SANZ</t>
+          <t>P. MARTINEZ FERIA</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1234,78 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8805</v>
+        <v>-1.0061</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.8618</v>
+        <v>0.6533</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.0186</v>
+        <v>-1.6594</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.8838</v>
+        <v>-0.5441</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.614</v>
+        <v>-0.8138</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.2698</v>
+        <v>0.2696</v>
       </c>
       <c r="J10" t="n">
-        <v>0</v>
+        <v>0.3492</v>
       </c>
       <c r="K10" t="n">
-        <v>0</v>
+        <v>0.3492</v>
       </c>
       <c r="L10" t="n">
         <v>0</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.8838</v>
+        <v>-0.8933</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.614</v>
+        <v>-1.163</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.2698</v>
+        <v>0.2696</v>
       </c>
       <c r="P10" t="n">
-        <v>-0.9767</v>
+        <v>0.586</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0199</v>
+        <v>0.1706</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1149</v>
+        <v>0.3041</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.1348</v>
+        <v>-0.1335</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>F. LLORENS LLAURADO</t>
+          <t>B. ROS FERNANDEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1317,78 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.972</v>
+        <v>-1.8342</v>
       </c>
       <c r="E11" t="n">
-        <v>-1.9435</v>
+        <v>0.4454</v>
       </c>
       <c r="F11" t="n">
-        <v>-0.0286</v>
+        <v>-2.2796</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.6982</v>
+        <v>-0.901</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.2553</v>
+        <v>-0.8066</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.4429</v>
+        <v>-0.0944</v>
       </c>
       <c r="J11" t="n">
-        <v>-1.2041</v>
+        <v>-0.5518</v>
       </c>
       <c r="K11" t="n">
-        <v>0.1036</v>
+        <v>0.0819</v>
       </c>
       <c r="L11" t="n">
-        <v>-1.3077</v>
+        <v>-0.6336000000000001</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4941</v>
+        <v>-0.3492</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.3589</v>
+        <v>-0.8885</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.1352</v>
+        <v>0.5393</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.586</v>
+        <v>0.9767</v>
       </c>
       <c r="Q11" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>0.3907</v>
+        <v>0.9767</v>
       </c>
       <c r="S11" t="n">
-        <v>0.5895</v>
+        <v>-0.4141</v>
       </c>
       <c r="T11" t="n">
-        <v>0.2374</v>
+        <v>-0.2214</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3521</v>
+        <v>-0.1926</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.2772</v>
+        <v>-1.4959</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.2186</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.2772</v>
+        <v>-2.7145</v>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. PÉREZ GALINDO</t>
+          <t>P. MONSALVE SANZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1400,78 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.5862</v>
+        <v>-1.8805</v>
       </c>
       <c r="E12" t="n">
-        <v>-4.4955</v>
+        <v>-0.8618</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9093</v>
+        <v>-1.0186</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.9468</v>
+        <v>-0.8838</v>
       </c>
       <c r="H12" t="n">
-        <v>-3.054</v>
+        <v>-0.614</v>
       </c>
       <c r="I12" t="n">
-        <v>1.1072</v>
+        <v>-0.2698</v>
       </c>
       <c r="J12" t="n">
-        <v>-1.7681</v>
+        <v>0</v>
       </c>
       <c r="K12" t="n">
-        <v>-1.5273</v>
+        <v>0</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.2408</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.1787</v>
+        <v>-0.8838</v>
       </c>
       <c r="N12" t="n">
-        <v>-1.5267</v>
+        <v>-0.614</v>
       </c>
       <c r="O12" t="n">
-        <v>1.348</v>
+        <v>-0.2698</v>
       </c>
       <c r="P12" t="n">
-        <v>-1.1721</v>
+        <v>-0.9767</v>
       </c>
       <c r="Q12" t="n">
-        <v>-2.9301</v>
+        <v>-0.9767</v>
       </c>
       <c r="R12" t="n">
-        <v>1.7581</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>0.9196</v>
+        <v>-0.0199</v>
       </c>
       <c r="T12" t="n">
-        <v>0.5897</v>
+        <v>0.1149</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3299</v>
+        <v>-0.1348</v>
       </c>
       <c r="V12" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>-0.3869</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
         <v>0</v>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>F. LLORENS LLAURADO</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,229 +1483,240 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-0.8145999999999995</v>
+        <v>-1.972</v>
       </c>
       <c r="E13" t="n">
-        <v>0.1742000000000008</v>
+        <v>-1.9435</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.9886999999999997</v>
+        <v>-0.0286</v>
       </c>
       <c r="G13" t="n">
-        <v>-8.461499999999999</v>
+        <v>-1.6982</v>
       </c>
       <c r="H13" t="n">
-        <v>-9.8109</v>
+        <v>-0.2553</v>
       </c>
       <c r="I13" t="n">
-        <v>1.3492</v>
+        <v>-1.4429</v>
       </c>
       <c r="J13" t="n">
-        <v>-3.773500000000001</v>
+        <v>-1.2041</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2669999999999995</v>
+        <v>0.1036</v>
       </c>
       <c r="L13" t="n">
-        <v>-4.0406</v>
+        <v>-1.3077</v>
       </c>
       <c r="M13" t="n">
-        <v>-4.688</v>
+        <v>-0.4941</v>
       </c>
       <c r="N13" t="n">
-        <v>-10.0779</v>
+        <v>-0.3589</v>
       </c>
       <c r="O13" t="n">
-        <v>5.389799999999999</v>
+        <v>-0.1352</v>
       </c>
       <c r="P13" t="n">
-        <v>-0.9768999999999999</v>
+        <v>-0.586</v>
       </c>
       <c r="Q13" t="n">
-        <v>-11.7204</v>
+        <v>-0.9767</v>
       </c>
       <c r="R13" t="n">
-        <v>10.7438</v>
+        <v>0.3907</v>
       </c>
       <c r="S13" t="n">
-        <v>6.7409</v>
+        <v>0.5895</v>
       </c>
       <c r="T13" t="n">
-        <v>5.751899999999999</v>
+        <v>0.2374</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9893000000000001</v>
+        <v>0.3521</v>
       </c>
       <c r="V13" t="n">
-        <v>1.8828</v>
+        <v>-0.2772</v>
       </c>
       <c r="W13" t="n">
-        <v>9.916499999999999</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>-8.033700000000001</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>M. BATALLER LOPEZ</t>
+          <t>R. PEREZ GALINDO</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C14" t="n">
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>7.5973</v>
+        <v>-3.5002</v>
       </c>
       <c r="E14" t="n">
-        <v>7.1572</v>
+        <v>-5.4095</v>
       </c>
       <c r="F14" t="n">
-        <v>0.4401</v>
+        <v>1.9093</v>
       </c>
       <c r="G14" t="n">
-        <v>5.2971</v>
+        <v>-2.8608</v>
       </c>
       <c r="H14" t="n">
-        <v>4.205</v>
+        <v>-3.361</v>
       </c>
       <c r="I14" t="n">
-        <v>1.0922</v>
+        <v>0.5002</v>
       </c>
       <c r="J14" t="n">
-        <v>4.4677</v>
+        <v>-2.6821</v>
       </c>
       <c r="K14" t="n">
-        <v>3.914</v>
+        <v>-1.8343</v>
       </c>
       <c r="L14" t="n">
-        <v>0.5537</v>
+        <v>-0.8478</v>
       </c>
       <c r="M14" t="n">
-        <v>0.8294</v>
+        <v>-0.1787</v>
       </c>
       <c r="N14" t="n">
-        <v>0.2909</v>
+        <v>-1.5267</v>
       </c>
       <c r="O14" t="n">
-        <v>0.5385</v>
+        <v>1.348</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.1953</v>
+        <v>-1.1721</v>
       </c>
       <c r="Q14" t="n">
-        <v>-1.9534</v>
+        <v>-2.9301</v>
       </c>
       <c r="R14" t="n">
         <v>1.7581</v>
       </c>
       <c r="S14" t="n">
-        <v>-1.4376</v>
+        <v>0.9196</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5088</v>
+        <v>0.5897</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.9288</v>
+        <v>0.3299</v>
       </c>
       <c r="V14" t="n">
-        <v>3.9331</v>
+        <v>-0.3869</v>
       </c>
       <c r="W14" t="n">
-        <v>5.1517</v>
+        <v>-0.3869</v>
       </c>
       <c r="X14" t="n">
-        <v>-1.2186</v>
+        <v>0</v>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>G. ALBA ASTOLA</t>
+          <t>--- TOTAL ---</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CB NAVÀS VISCOLA</t>
+          <t>CB. CORNELLÀ</t>
         </is>
       </c>
       <c r="C15" t="n">
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.5274</v>
+        <v>-0.8146000000000013</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0162</v>
+        <v>0.1742000000000008</v>
       </c>
       <c r="F15" t="n">
-        <v>1.5113</v>
+        <v>-0.9886999999999997</v>
       </c>
       <c r="G15" t="n">
-        <v>0.2996</v>
+        <v>-8.461499999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>-1.1039</v>
+        <v>-9.8109</v>
       </c>
       <c r="I15" t="n">
-        <v>1.4035</v>
+        <v>1.3492</v>
       </c>
       <c r="J15" t="n">
-        <v>0.4637</v>
+        <v>-3.773500000000001</v>
       </c>
       <c r="K15" t="n">
-        <v>0.0038</v>
+        <v>0.2670000000000001</v>
       </c>
       <c r="L15" t="n">
-        <v>0.4599</v>
+        <v>-4.040500000000001</v>
       </c>
       <c r="M15" t="n">
-        <v>-0.1641</v>
+        <v>-4.688</v>
       </c>
       <c r="N15" t="n">
-        <v>-1.1077</v>
+        <v>-10.0779</v>
       </c>
       <c r="O15" t="n">
-        <v>0.9435</v>
+        <v>5.3898</v>
       </c>
       <c r="P15" t="n">
-        <v>1.7581</v>
+        <v>-0.9768999999999999</v>
       </c>
       <c r="Q15" t="n">
-        <v>0</v>
+        <v>-11.7204</v>
       </c>
       <c r="R15" t="n">
-        <v>1.7581</v>
+        <v>10.7438</v>
       </c>
       <c r="S15" t="n">
-        <v>-0.0261</v>
+        <v>6.740900000000001</v>
       </c>
       <c r="T15" t="n">
-        <v>0.0566</v>
+        <v>5.751899999999999</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.08260000000000001</v>
+        <v>0.9893000000000001</v>
       </c>
       <c r="V15" t="n">
-        <v>1.4959</v>
+        <v>1.8828</v>
       </c>
       <c r="W15" t="n">
-        <v>1.4959</v>
+        <v>9.916499999999999</v>
       </c>
       <c r="X15" t="n">
-        <v>0</v>
-      </c>
+        <v>-8.0337</v>
+      </c>
+      <c r="Y15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>H. LOUASSA</t>
+          <t>M. BATALLER LOPEZ</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,73 +1728,78 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>1.2558</v>
+        <v>7.5973</v>
       </c>
       <c r="E16" t="n">
-        <v>0.3084</v>
+        <v>7.1572</v>
       </c>
       <c r="F16" t="n">
-        <v>0.9474</v>
+        <v>0.4401</v>
       </c>
       <c r="G16" t="n">
-        <v>0.9883</v>
+        <v>5.2971</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8534</v>
+        <v>4.205</v>
       </c>
       <c r="I16" t="n">
-        <v>0.1348</v>
+        <v>1.0922</v>
       </c>
       <c r="J16" t="n">
-        <v>0.3888</v>
+        <v>4.4677</v>
       </c>
       <c r="K16" t="n">
-        <v>0.3888</v>
+        <v>3.914</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>0.5537</v>
       </c>
       <c r="M16" t="n">
-        <v>0.5994</v>
+        <v>0.8294</v>
       </c>
       <c r="N16" t="n">
-        <v>0.4646</v>
+        <v>0.2909</v>
       </c>
       <c r="O16" t="n">
-        <v>0.1348</v>
+        <v>0.5385</v>
       </c>
       <c r="P16" t="n">
-        <v>0.3907</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q16" t="n">
-        <v>0</v>
+        <v>-1.9534</v>
       </c>
       <c r="R16" t="n">
-        <v>0.3907</v>
+        <v>1.7581</v>
       </c>
       <c r="S16" t="n">
-        <v>-0.1231</v>
+        <v>-1.4376</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0805</v>
+        <v>-0.5088</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.0427</v>
+        <v>-0.9288</v>
       </c>
       <c r="V16" t="n">
-        <v>0</v>
+        <v>3.9331</v>
       </c>
       <c r="W16" t="n">
-        <v>0</v>
+        <v>5.1517</v>
       </c>
       <c r="X16" t="n">
-        <v>0</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>A. KEITA</t>
+          <t>G. ALBA ASTOLA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1811,78 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>0.6256</v>
+        <v>3.5274</v>
       </c>
       <c r="E17" t="n">
-        <v>-1.6945</v>
+        <v>2.0162</v>
       </c>
       <c r="F17" t="n">
-        <v>2.3201</v>
+        <v>1.5113</v>
       </c>
       <c r="G17" t="n">
-        <v>3.2193</v>
+        <v>0.2996</v>
       </c>
       <c r="H17" t="n">
-        <v>2.02</v>
+        <v>-1.1039</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1994</v>
+        <v>1.4035</v>
       </c>
       <c r="J17" t="n">
-        <v>2.4596</v>
+        <v>0.4637</v>
       </c>
       <c r="K17" t="n">
-        <v>2.3382</v>
+        <v>0.0038</v>
       </c>
       <c r="L17" t="n">
-        <v>0.1214</v>
+        <v>0.4599</v>
       </c>
       <c r="M17" t="n">
-        <v>0.7598</v>
+        <v>-0.1641</v>
       </c>
       <c r="N17" t="n">
-        <v>-0.3182</v>
+        <v>-1.1077</v>
       </c>
       <c r="O17" t="n">
-        <v>1.078</v>
+        <v>0.9435</v>
       </c>
       <c r="P17" t="n">
-        <v>-1.5627</v>
+        <v>1.7581</v>
       </c>
       <c r="Q17" t="n">
-        <v>-3.9069</v>
+        <v>0</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3441</v>
+        <v>1.7581</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.4217</v>
+        <v>-0.0261</v>
       </c>
       <c r="T17" t="n">
-        <v>0.0848</v>
+        <v>0.0566</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.5065</v>
+        <v>-0.08260000000000001</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.6093</v>
+        <v>1.4959</v>
       </c>
       <c r="W17" t="n">
-        <v>-0.3321</v>
+        <v>1.4959</v>
       </c>
       <c r="X17" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>D. ZHURAVLOV</t>
+          <t>H. LOUASSA</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1894,78 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>0.5693</v>
+        <v>1.2558</v>
       </c>
       <c r="E18" t="n">
-        <v>1.378</v>
+        <v>0.3084</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.8087</v>
+        <v>0.9474</v>
       </c>
       <c r="G18" t="n">
-        <v>1.9458</v>
+        <v>0.9883</v>
       </c>
       <c r="H18" t="n">
-        <v>3.1599</v>
+        <v>0.8534</v>
       </c>
       <c r="I18" t="n">
-        <v>-1.2142</v>
+        <v>0.1348</v>
       </c>
       <c r="J18" t="n">
-        <v>1.7012</v>
+        <v>0.3888</v>
       </c>
       <c r="K18" t="n">
-        <v>2.3753</v>
+        <v>0.3888</v>
       </c>
       <c r="L18" t="n">
-        <v>-0.6741</v>
+        <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.2446</v>
+        <v>0.5994</v>
       </c>
       <c r="N18" t="n">
-        <v>0.7846</v>
+        <v>0.4646</v>
       </c>
       <c r="O18" t="n">
-        <v>-0.5401</v>
+        <v>0.1348</v>
       </c>
       <c r="P18" t="n">
-        <v>-0.1953</v>
+        <v>0.3907</v>
       </c>
       <c r="Q18" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R18" t="n">
-        <v>0.7814</v>
+        <v>0.3907</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.9039</v>
+        <v>-0.1231</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.5103</v>
+        <v>-0.0805</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.3936</v>
+        <v>-0.0427</v>
       </c>
       <c r="V18" t="n">
-        <v>-0.2772</v>
+        <v>0</v>
       </c>
       <c r="W18" t="n">
-        <v>1.1638</v>
+        <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.441</v>
+        <v>0</v>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>A. SALO BLAYA</t>
+          <t>A. KEITA</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1977,78 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.6435</v>
+        <v>0.6256</v>
       </c>
       <c r="E19" t="n">
-        <v>0.288</v>
+        <v>-1.6945</v>
       </c>
       <c r="F19" t="n">
-        <v>-0.9315</v>
+        <v>2.3201</v>
       </c>
       <c r="G19" t="n">
-        <v>-0.3604</v>
+        <v>3.2193</v>
       </c>
       <c r="H19" t="n">
-        <v>-0.6705</v>
+        <v>2.02</v>
       </c>
       <c r="I19" t="n">
-        <v>0.3101</v>
+        <v>1.1994</v>
       </c>
       <c r="J19" t="n">
-        <v>-0.2857</v>
+        <v>2.4596</v>
       </c>
       <c r="K19" t="n">
-        <v>-0.3262</v>
+        <v>2.3382</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0405</v>
+        <v>0.1214</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.0747</v>
+        <v>0.7598</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3443</v>
+        <v>-0.3182</v>
       </c>
       <c r="O19" t="n">
-        <v>0.2696</v>
+        <v>1.078</v>
       </c>
       <c r="P19" t="n">
-        <v>0.586</v>
+        <v>-1.5627</v>
       </c>
       <c r="Q19" t="n">
-        <v>0</v>
+        <v>-3.9069</v>
       </c>
       <c r="R19" t="n">
-        <v>0.586</v>
+        <v>2.3441</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3495</v>
+        <v>-0.4217</v>
       </c>
       <c r="T19" t="n">
-        <v>0.5737</v>
+        <v>0.0848</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.2242</v>
+        <v>-0.5065</v>
       </c>
       <c r="V19" t="n">
-        <v>-1.2186</v>
+        <v>-0.6093</v>
       </c>
       <c r="W19" t="n">
-        <v>0</v>
+        <v>-0.3321</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.2186</v>
+        <v>-0.2772</v>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. FALL</t>
+          <t>D. ZHURAVLOV</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +2060,72 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.3665</v>
+        <v>0.5693</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.135</v>
+        <v>1.378</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.2315</v>
+        <v>-0.8087</v>
       </c>
       <c r="G20" t="n">
-        <v>1.6519</v>
+        <v>1.9458</v>
       </c>
       <c r="H20" t="n">
-        <v>0.1553</v>
+        <v>3.1599</v>
       </c>
       <c r="I20" t="n">
-        <v>1.4966</v>
+        <v>-1.2142</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7927999999999999</v>
+        <v>1.7012</v>
       </c>
       <c r="K20" t="n">
-        <v>0.1049</v>
+        <v>2.3753</v>
       </c>
       <c r="L20" t="n">
-        <v>0.6879</v>
+        <v>-0.6741</v>
       </c>
       <c r="M20" t="n">
-        <v>0.8591</v>
+        <v>0.2446</v>
       </c>
       <c r="N20" t="n">
-        <v>0.0504</v>
+        <v>0.7846</v>
       </c>
       <c r="O20" t="n">
-        <v>0.8087</v>
+        <v>-0.5401</v>
       </c>
       <c r="P20" t="n">
-        <v>0</v>
+        <v>-0.1953</v>
       </c>
       <c r="Q20" t="n">
         <v>-0.9767</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9767</v>
+        <v>0.7814</v>
       </c>
       <c r="S20" t="n">
-        <v>0.0282</v>
+        <v>-0.9039</v>
       </c>
       <c r="T20" t="n">
-        <v>0.0489</v>
+        <v>-0.5103</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.0208</v>
+        <v>-0.3936</v>
       </c>
       <c r="V20" t="n">
-        <v>-3.0466</v>
+        <v>-0.2772</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>1.1638</v>
       </c>
       <c r="X20" t="n">
-        <v>-3.0466</v>
+        <v>-1.441</v>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="21">
@@ -2047,73 +2143,78 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.1656</v>
+        <v>0.307</v>
       </c>
       <c r="E21" t="n">
-        <v>-3.2881</v>
+        <v>0.307</v>
       </c>
       <c r="F21" t="n">
-        <v>1.1225</v>
+        <v>0</v>
       </c>
       <c r="G21" t="n">
-        <v>-1.8665</v>
+        <v>0.307</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.2346</v>
+        <v>0.307</v>
       </c>
       <c r="I21" t="n">
-        <v>-1.6319</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
-        <v>-2.5661</v>
+        <v>0.307</v>
       </c>
       <c r="K21" t="n">
-        <v>0.0089</v>
+        <v>0.307</v>
       </c>
       <c r="L21" t="n">
-        <v>-2.575</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6997</v>
+        <v>0</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.2435</v>
+        <v>0</v>
       </c>
       <c r="O21" t="n">
-        <v>0.9431</v>
+        <v>0</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9767</v>
+        <v>0</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9767</v>
+        <v>0</v>
       </c>
       <c r="R21" t="n">
-        <v>1.9534</v>
+        <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.9437</v>
+        <v>0</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.2997</v>
+        <v>0</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.6441</v>
+        <v>0</v>
       </c>
       <c r="V21" t="n">
-        <v>-0.3321</v>
+        <v>0</v>
       </c>
       <c r="W21" t="n">
-        <v>0.5545</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-0.8865</v>
+        <v>0</v>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>I. JUNCADELLA ENFEDAQUE</t>
+          <t>A. SALO BLAYA</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2226,78 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-2.316</v>
+        <v>-0.6435</v>
       </c>
       <c r="E22" t="n">
-        <v>-1.4482</v>
+        <v>0.288</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.8677</v>
+        <v>-0.9315</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.3868</v>
+        <v>-0.3604</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.1734</v>
+        <v>-0.6705</v>
       </c>
       <c r="I22" t="n">
-        <v>-1.2134</v>
+        <v>0.3101</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.3073</v>
+        <v>-0.2857</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0409</v>
+        <v>-0.3262</v>
       </c>
       <c r="L22" t="n">
-        <v>-1.3482</v>
+        <v>0.0405</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.0795</v>
+        <v>-0.0747</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.2144</v>
+        <v>-0.3443</v>
       </c>
       <c r="O22" t="n">
-        <v>0.1348</v>
+        <v>0.2696</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="Q22" t="n">
         <v>0</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>0.586</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.3198</v>
+        <v>0.3495</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.141</v>
+        <v>0.5737</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.1789</v>
+        <v>-0.2242</v>
       </c>
       <c r="V22" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>-0.6093</v>
+        <v>-1.2186</v>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>A. MONTAGUT PUNTI</t>
+          <t>A. FALL</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2309,78 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-4.247</v>
+        <v>-1.3665</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.5932</v>
+        <v>-0.135</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.6538</v>
+        <v>-1.2315</v>
       </c>
       <c r="G23" t="n">
-        <v>-1.3267</v>
+        <v>1.6519</v>
       </c>
       <c r="H23" t="n">
-        <v>1.5997</v>
+        <v>0.1553</v>
       </c>
       <c r="I23" t="n">
-        <v>-2.9264</v>
+        <v>1.4966</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.4267</v>
+        <v>0.7927999999999999</v>
       </c>
       <c r="K23" t="n">
-        <v>1.2292</v>
+        <v>0.1049</v>
       </c>
       <c r="L23" t="n">
-        <v>-2.6559</v>
+        <v>0.6879</v>
       </c>
       <c r="M23" t="n">
-        <v>0.1</v>
+        <v>0.8591</v>
       </c>
       <c r="N23" t="n">
-        <v>0.3705</v>
+        <v>0.0504</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.2704</v>
+        <v>0.8087</v>
       </c>
       <c r="P23" t="n">
-        <v>-0.7814</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.9534</v>
+        <v>-0.9767</v>
       </c>
       <c r="R23" t="n">
-        <v>1.1721</v>
+        <v>0.9767</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.9204</v>
+        <v>0.0282</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.2131</v>
+        <v>0.0489</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.7073</v>
+        <v>-0.0208</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.2186</v>
+        <v>-3.0466</v>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>--- TOTAL ---</t>
+          <t>I. JUNCADELLA ENFEDAQUE</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,68 +2392,318 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>2.836800000000001</v>
+        <v>-2.316</v>
       </c>
       <c r="E24" t="n">
-        <v>0.988799999999999</v>
+        <v>-1.4482</v>
       </c>
       <c r="F24" t="n">
-        <v>1.8482</v>
+        <v>-0.8677</v>
       </c>
       <c r="G24" t="n">
+        <v>-1.3868</v>
+      </c>
+      <c r="H24" t="n">
+        <v>-0.1734</v>
+      </c>
+      <c r="I24" t="n">
+        <v>-1.2134</v>
+      </c>
+      <c r="J24" t="n">
+        <v>-1.3073</v>
+      </c>
+      <c r="K24" t="n">
+        <v>0.0409</v>
+      </c>
+      <c r="L24" t="n">
+        <v>-1.3482</v>
+      </c>
+      <c r="M24" t="n">
+        <v>-0.0795</v>
+      </c>
+      <c r="N24" t="n">
+        <v>-0.2144</v>
+      </c>
+      <c r="O24" t="n">
+        <v>0.1348</v>
+      </c>
+      <c r="P24" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q24" t="n">
+        <v>0</v>
+      </c>
+      <c r="R24" t="n">
+        <v>0</v>
+      </c>
+      <c r="S24" t="n">
+        <v>-0.3198</v>
+      </c>
+      <c r="T24" t="n">
+        <v>-0.141</v>
+      </c>
+      <c r="U24" t="n">
+        <v>-0.1789</v>
+      </c>
+      <c r="V24" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="W24" t="n">
+        <v>0</v>
+      </c>
+      <c r="X24" t="n">
+        <v>-0.6093</v>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>P. MONES RIERA</t>
+        </is>
+      </c>
+      <c r="B25" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C25" t="n">
+        <v>1</v>
+      </c>
+      <c r="D25" t="n">
+        <v>-2.4726</v>
+      </c>
+      <c r="E25" t="n">
+        <v>-3.595</v>
+      </c>
+      <c r="F25" t="n">
+        <v>1.1225</v>
+      </c>
+      <c r="G25" t="n">
+        <v>-2.1735</v>
+      </c>
+      <c r="H25" t="n">
+        <v>-0.5416</v>
+      </c>
+      <c r="I25" t="n">
+        <v>-1.6319</v>
+      </c>
+      <c r="J25" t="n">
+        <v>-2.8731</v>
+      </c>
+      <c r="K25" t="n">
+        <v>-0.2981</v>
+      </c>
+      <c r="L25" t="n">
+        <v>-2.575</v>
+      </c>
+      <c r="M25" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="N25" t="n">
+        <v>-0.2435</v>
+      </c>
+      <c r="O25" t="n">
+        <v>0.9431</v>
+      </c>
+      <c r="P25" t="n">
+        <v>0.9767</v>
+      </c>
+      <c r="Q25" t="n">
+        <v>-0.9767</v>
+      </c>
+      <c r="R25" t="n">
+        <v>1.9534</v>
+      </c>
+      <c r="S25" t="n">
+        <v>-0.9437</v>
+      </c>
+      <c r="T25" t="n">
+        <v>-0.2997</v>
+      </c>
+      <c r="U25" t="n">
+        <v>-0.6441</v>
+      </c>
+      <c r="V25" t="n">
+        <v>-0.3321</v>
+      </c>
+      <c r="W25" t="n">
+        <v>0.5545</v>
+      </c>
+      <c r="X25" t="n">
+        <v>-0.8865</v>
+      </c>
+      <c r="Y25" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>A. MONTAGUT PUNTI</t>
+        </is>
+      </c>
+      <c r="B26" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C26" t="n">
+        <v>1</v>
+      </c>
+      <c r="D26" t="n">
+        <v>-4.247</v>
+      </c>
+      <c r="E26" t="n">
+        <v>-3.5932</v>
+      </c>
+      <c r="F26" t="n">
+        <v>-0.6538</v>
+      </c>
+      <c r="G26" t="n">
+        <v>-1.3267</v>
+      </c>
+      <c r="H26" t="n">
+        <v>1.5997</v>
+      </c>
+      <c r="I26" t="n">
+        <v>-2.9264</v>
+      </c>
+      <c r="J26" t="n">
+        <v>-1.4267</v>
+      </c>
+      <c r="K26" t="n">
+        <v>1.2292</v>
+      </c>
+      <c r="L26" t="n">
+        <v>-2.6559</v>
+      </c>
+      <c r="M26" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N26" t="n">
+        <v>0.3705</v>
+      </c>
+      <c r="O26" t="n">
+        <v>-0.2704</v>
+      </c>
+      <c r="P26" t="n">
+        <v>-0.7814</v>
+      </c>
+      <c r="Q26" t="n">
+        <v>-1.9534</v>
+      </c>
+      <c r="R26" t="n">
+        <v>1.1721</v>
+      </c>
+      <c r="S26" t="n">
+        <v>-0.9204</v>
+      </c>
+      <c r="T26" t="n">
+        <v>-0.2131</v>
+      </c>
+      <c r="U26" t="n">
+        <v>-0.7073</v>
+      </c>
+      <c r="V26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="W26" t="n">
+        <v>0</v>
+      </c>
+      <c r="X26" t="n">
+        <v>-1.2186</v>
+      </c>
+      <c r="Y26" t="inlineStr">
+        <is>
+          <t>play_by_play_2484310_PROCESSED_CHRONO.xlsx</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>--- TOTAL ---</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>CB NAVÀS VISCOLA</t>
+        </is>
+      </c>
+      <c r="C27" t="n">
+        <v>1</v>
+      </c>
+      <c r="D27" t="n">
+        <v>2.8368</v>
+      </c>
+      <c r="E27" t="n">
+        <v>0.9888999999999988</v>
+      </c>
+      <c r="F27" t="n">
+        <v>1.848199999999999</v>
+      </c>
+      <c r="G27" t="n">
         <v>8.461599999999999</v>
       </c>
-      <c r="H24" t="n">
-        <v>9.810899999999998</v>
-      </c>
-      <c r="I24" t="n">
+      <c r="H27" t="n">
+        <v>9.8109</v>
+      </c>
+      <c r="I27" t="n">
         <v>-1.349299999999999</v>
       </c>
-      <c r="J24" t="n">
+      <c r="J27" t="n">
         <v>4.688</v>
       </c>
-      <c r="K24" t="n">
+      <c r="K27" t="n">
         <v>10.0778</v>
       </c>
-      <c r="L24" t="n">
+      <c r="L27" t="n">
         <v>-5.3898</v>
       </c>
-      <c r="M24" t="n">
+      <c r="M27" t="n">
         <v>3.7737</v>
       </c>
-      <c r="N24" t="n">
+      <c r="N27" t="n">
         <v>-0.2670999999999999</v>
       </c>
-      <c r="O24" t="n">
+      <c r="O27" t="n">
         <v>4.0405</v>
       </c>
-      <c r="P24" t="n">
+      <c r="P27" t="n">
         <v>0.9768</v>
       </c>
-      <c r="Q24" t="n">
+      <c r="Q27" t="n">
         <v>-10.7438</v>
       </c>
-      <c r="R24" t="n">
+      <c r="R27" t="n">
         <v>11.7206</v>
       </c>
-      <c r="S24" t="n">
-        <v>-4.7186</v>
-      </c>
-      <c r="T24" t="n">
+      <c r="S27" t="n">
+        <v>-4.718599999999999</v>
+      </c>
+      <c r="T27" t="n">
         <v>-0.9894000000000001</v>
       </c>
-      <c r="U24" t="n">
+      <c r="U27" t="n">
         <v>-3.7295</v>
       </c>
-      <c r="V24" t="n">
+      <c r="V27" t="n">
         <v>-1.8827</v>
       </c>
-      <c r="W24" t="n">
+      <c r="W27" t="n">
         <v>8.033799999999999</v>
       </c>
-      <c r="X24" t="n">
-        <v>-9.916399999999999</v>
-      </c>
+      <c r="X27" t="n">
+        <v>-9.916400000000001</v>
+      </c>
+      <c r="Y27" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
